--- a/rtss-pre1917/src/main/resources/excel-templates/birth-death-counts-ugvi-csk.xlsx
+++ b/rtss-pre1917/src/main/resources/excel-templates/birth-death-counts-ugvi-csk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA532E8A-B5E7-4C17-A51E-D6E2AE0F6E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9526782C-27CF-441E-AB4F-CF40893D4DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{552C350D-897F-4D5C-BE01-5853E10F71A5}"/>
   </bookViews>
@@ -154,13 +154,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1318,8 +1318,8 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="00B0F0"/>
@@ -1335,8 +1335,8 @@
           <c:dPt>
             <c:idx val="5"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
+              <c:symbol val="diamond"/>
+              <c:size val="8"/>
               <c:spPr>
                 <a:solidFill>
                   <a:srgbClr val="00B0F0"/>
@@ -1517,8 +1517,8 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent2">
@@ -1692,8 +1692,8 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="00B050"/>
@@ -1709,8 +1709,8 @@
           <c:dPt>
             <c:idx val="5"/>
             <c:marker>
-              <c:symbol val="circle"/>
-              <c:size val="5"/>
+              <c:symbol val="diamond"/>
+              <c:size val="8"/>
               <c:spPr>
                 <a:solidFill>
                   <a:srgbClr val="00B050"/>
@@ -1888,8 +1888,8 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
@@ -3201,65 +3201,65 @@
     </row>
     <row r="3" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A3" s="4"/>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
     </row>
     <row r="4" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A4" s="4"/>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5" t="s">
+      <c r="H4" s="8"/>
+      <c r="I4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="5"/>
+      <c r="J4" s="8"/>
     </row>
     <row r="5" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A5" s="4"/>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="4"/>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="AE5" s="3"/>
@@ -3268,19 +3268,19 @@
       <c r="AH5" s="3"/>
     </row>
     <row r="6" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>1880</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>1000</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>700</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>1100</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <v>800</v>
       </c>
       <c r="F6" s="4"/>
@@ -3294,20 +3294,20 @@
       <c r="AH6" s="3"/>
     </row>
     <row r="7" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <f>A6+1</f>
         <v>1881</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>1010</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>710</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>1110</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <v>810</v>
       </c>
       <c r="F7" s="4"/>
@@ -3321,20 +3321,20 @@
       <c r="AH7" s="3"/>
     </row>
     <row r="8" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <f t="shared" ref="A8:A40" si="0">A7+1</f>
         <v>1882</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>1020</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>720</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>1120</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <v>820</v>
       </c>
       <c r="F8" s="4"/>
@@ -3348,20 +3348,20 @@
       <c r="AH8" s="3"/>
     </row>
     <row r="9" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A9" s="7">
+      <c r="A9" s="6">
         <f t="shared" si="0"/>
         <v>1883</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <v>1030</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>730</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>1130</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <v>830</v>
       </c>
       <c r="F9" s="4"/>
@@ -3375,20 +3375,20 @@
       <c r="AH9" s="3"/>
     </row>
     <row r="10" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A10" s="7">
+      <c r="A10" s="6">
         <f t="shared" si="0"/>
         <v>1884</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <v>1040</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>740</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>1140</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <v>840</v>
       </c>
       <c r="F10" s="4"/>
@@ -3402,33 +3402,33 @@
       <c r="AH10" s="3"/>
     </row>
     <row r="11" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A11" s="7">
+      <c r="A11" s="6">
         <f t="shared" si="0"/>
         <v>1885</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>1050</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>750</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <v>1150</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <v>850</v>
       </c>
       <c r="F11" s="4"/>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <v>1200</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <v>1350</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="7">
         <v>900</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="7">
         <v>1250</v>
       </c>
       <c r="AE11" s="3"/>
@@ -3437,30 +3437,30 @@
       <c r="AH11" s="3"/>
     </row>
     <row r="12" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A12" s="7">
+      <c r="A12" s="6">
         <f t="shared" si="0"/>
         <v>1886</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <v>1060</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>760</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <v>1160</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="7">
         <v>860</v>
       </c>
       <c r="F12" s="4"/>
-      <c r="G12" s="8">
+      <c r="G12" s="7">
         <v>1500</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="7">
         <v>1200</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="7">
         <v>1200</v>
       </c>
       <c r="J12" s="4">
@@ -3472,20 +3472,20 @@
       <c r="AH12" s="3"/>
     </row>
     <row r="13" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A13" s="7">
+      <c r="A13" s="6">
         <f t="shared" si="0"/>
         <v>1887</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <v>1070</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>770</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>1170</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="7">
         <v>870</v>
       </c>
       <c r="F13" s="4"/>
@@ -3503,20 +3503,20 @@
       <c r="AH13" s="3"/>
     </row>
     <row r="14" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A14" s="7">
+      <c r="A14" s="6">
         <f t="shared" si="0"/>
         <v>1888</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="7">
         <v>1080</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>780</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <v>1180</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="7">
         <v>880</v>
       </c>
       <c r="F14" s="4"/>
@@ -3530,20 +3530,20 @@
       <c r="AH14" s="3"/>
     </row>
     <row r="15" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A15" s="7">
+      <c r="A15" s="6">
         <f t="shared" si="0"/>
         <v>1889</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>1090</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>790</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <v>1190</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="7">
         <v>890</v>
       </c>
       <c r="F15" s="4"/>
@@ -3557,20 +3557,20 @@
       <c r="AH15" s="3"/>
     </row>
     <row r="16" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A16" s="7">
+      <c r="A16" s="6">
         <f t="shared" si="0"/>
         <v>1890</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="7">
         <v>1100</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <v>800</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <v>1200</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="7">
         <v>900</v>
       </c>
       <c r="F16" s="4"/>
@@ -3584,20 +3584,20 @@
       <c r="AH16" s="3"/>
     </row>
     <row r="17" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A17" s="7">
+      <c r="A17" s="6">
         <f t="shared" si="0"/>
         <v>1891</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="7">
         <v>1110</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>810</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>1210</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="7">
         <v>910</v>
       </c>
       <c r="F17" s="4"/>
@@ -3611,20 +3611,20 @@
       <c r="AH17" s="3"/>
     </row>
     <row r="18" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A18" s="7">
+      <c r="A18" s="6">
         <f t="shared" si="0"/>
         <v>1892</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="7">
         <v>1120</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>820</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>1220</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="7">
         <v>920</v>
       </c>
       <c r="F18" s="4"/>
@@ -3638,20 +3638,20 @@
       <c r="AH18" s="3"/>
     </row>
     <row r="19" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A19" s="7">
+      <c r="A19" s="6">
         <f t="shared" si="0"/>
         <v>1893</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="7">
         <v>1130</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <v>830</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <v>1230</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="7">
         <v>930</v>
       </c>
       <c r="F19" s="4"/>
@@ -3665,20 +3665,20 @@
       <c r="AH19" s="3"/>
     </row>
     <row r="20" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A20" s="7">
+      <c r="A20" s="6">
         <f t="shared" si="0"/>
         <v>1894</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="7">
         <v>1140</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="7">
         <v>840</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <v>1240</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="7">
         <v>940</v>
       </c>
       <c r="F20" s="4"/>
@@ -3692,20 +3692,20 @@
       <c r="AH20" s="3"/>
     </row>
     <row r="21" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A21" s="7">
+      <c r="A21" s="6">
         <f t="shared" si="0"/>
         <v>1895</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="7">
         <v>1150</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="7">
         <v>850</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <v>1250</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="7">
         <v>950</v>
       </c>
       <c r="F21" s="4"/>
@@ -3719,20 +3719,20 @@
       <c r="AH21" s="3"/>
     </row>
     <row r="22" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A22" s="7">
+      <c r="A22" s="6">
         <f t="shared" si="0"/>
         <v>1896</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="7">
         <v>1160</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="7">
         <v>860</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="7">
         <v>1260</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="7">
         <v>960</v>
       </c>
       <c r="F22" s="4"/>
@@ -3746,20 +3746,20 @@
       <c r="AH22" s="3"/>
     </row>
     <row r="23" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A23" s="7">
+      <c r="A23" s="6">
         <f t="shared" si="0"/>
         <v>1897</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="7">
         <v>1170</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="7">
         <v>870</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="7">
         <v>1270</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="7">
         <v>970</v>
       </c>
       <c r="F23" s="4"/>
@@ -3773,20 +3773,20 @@
       <c r="AH23" s="3"/>
     </row>
     <row r="24" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A24" s="7">
+      <c r="A24" s="6">
         <f t="shared" si="0"/>
         <v>1898</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="7">
         <v>1180</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="7">
         <v>880</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="7">
         <v>1280</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="7">
         <v>980</v>
       </c>
       <c r="F24" s="4"/>
@@ -3800,20 +3800,20 @@
       <c r="AH24" s="3"/>
     </row>
     <row r="25" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A25" s="7">
+      <c r="A25" s="6">
         <f t="shared" si="0"/>
         <v>1899</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="7">
         <v>1190</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="7">
         <v>890</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="7">
         <v>1290</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="7">
         <v>990</v>
       </c>
       <c r="F25" s="4"/>
@@ -3827,20 +3827,20 @@
       <c r="AH25" s="3"/>
     </row>
     <row r="26" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A26" s="7">
+      <c r="A26" s="6">
         <f t="shared" si="0"/>
         <v>1900</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="7">
         <v>1200</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="7">
         <v>900</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="7">
         <v>1300</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="7">
         <v>1000</v>
       </c>
       <c r="F26" s="4"/>
@@ -3854,20 +3854,20 @@
       <c r="AH26" s="3"/>
     </row>
     <row r="27" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A27" s="7">
+      <c r="A27" s="6">
         <f t="shared" si="0"/>
         <v>1901</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="7">
         <v>1210</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="7">
         <v>910</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="7">
         <v>1310</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="7">
         <v>1010</v>
       </c>
       <c r="F27" s="4"/>
@@ -3881,20 +3881,20 @@
       <c r="AH27" s="3"/>
     </row>
     <row r="28" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A28" s="7">
+      <c r="A28" s="6">
         <f t="shared" si="0"/>
         <v>1902</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="7">
         <v>1220</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="7">
         <v>920</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="7">
         <v>1320</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="7">
         <v>1020</v>
       </c>
       <c r="F28" s="4"/>
@@ -3908,20 +3908,20 @@
       <c r="AH28" s="3"/>
     </row>
     <row r="29" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A29" s="7">
+      <c r="A29" s="6">
         <f t="shared" si="0"/>
         <v>1903</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="7">
         <v>1230</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="7">
         <v>930</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="7">
         <v>1330</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="7">
         <v>1030</v>
       </c>
       <c r="F29" s="4"/>
@@ -3935,20 +3935,20 @@
       <c r="AH29" s="3"/>
     </row>
     <row r="30" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A30" s="7">
+      <c r="A30" s="6">
         <f t="shared" si="0"/>
         <v>1904</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="7">
         <v>1240</v>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="7">
         <v>940</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="7">
         <v>1340</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="7">
         <v>1040</v>
       </c>
       <c r="F30" s="4"/>
@@ -3962,20 +3962,20 @@
       <c r="AH30" s="3"/>
     </row>
     <row r="31" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A31" s="7">
+      <c r="A31" s="6">
         <f t="shared" si="0"/>
         <v>1905</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="7">
         <v>1250</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="7">
         <v>950</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="7">
         <v>1350</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="7">
         <v>1050</v>
       </c>
       <c r="F31" s="4"/>
@@ -3989,20 +3989,20 @@
       <c r="AH31" s="3"/>
     </row>
     <row r="32" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A32" s="7">
+      <c r="A32" s="6">
         <f t="shared" si="0"/>
         <v>1906</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="7">
         <v>1260</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="7">
         <v>960</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="7">
         <v>1360</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="7">
         <v>1060</v>
       </c>
       <c r="F32" s="4"/>
@@ -4016,20 +4016,20 @@
       <c r="AH32" s="3"/>
     </row>
     <row r="33" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A33" s="7">
+      <c r="A33" s="6">
         <f t="shared" si="0"/>
         <v>1907</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="7">
         <v>1270</v>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="7">
         <v>970</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="7">
         <v>1370</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="7">
         <v>1070</v>
       </c>
       <c r="F33" s="4"/>
@@ -4043,20 +4043,20 @@
       <c r="AH33" s="3"/>
     </row>
     <row r="34" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A34" s="7">
+      <c r="A34" s="6">
         <f t="shared" si="0"/>
         <v>1908</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="7">
         <v>1280</v>
       </c>
-      <c r="C34" s="8">
+      <c r="C34" s="7">
         <v>980</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="7">
         <v>1380</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="7">
         <v>1080</v>
       </c>
       <c r="F34" s="4"/>
@@ -4070,20 +4070,20 @@
       <c r="AH34" s="3"/>
     </row>
     <row r="35" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A35" s="7">
+      <c r="A35" s="6">
         <f t="shared" si="0"/>
         <v>1909</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="7">
         <v>1290</v>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="7">
         <v>990</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="7">
         <v>1390</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="7">
         <v>1090</v>
       </c>
       <c r="F35" s="4"/>
@@ -4097,20 +4097,20 @@
       <c r="AH35" s="3"/>
     </row>
     <row r="36" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A36" s="7">
+      <c r="A36" s="6">
         <f t="shared" si="0"/>
         <v>1910</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="7">
         <v>1300</v>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="7">
         <v>1000</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="7">
         <v>1400</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E36" s="7">
         <v>1100</v>
       </c>
       <c r="F36" s="4"/>
@@ -4124,20 +4124,20 @@
       <c r="AH36" s="3"/>
     </row>
     <row r="37" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A37" s="7">
+      <c r="A37" s="6">
         <f t="shared" si="0"/>
         <v>1911</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="7">
         <v>1310</v>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="7">
         <v>1010</v>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="7">
         <v>1410</v>
       </c>
-      <c r="E37" s="8">
+      <c r="E37" s="7">
         <v>1110</v>
       </c>
       <c r="F37" s="4"/>
@@ -4151,20 +4151,20 @@
       <c r="AH37" s="3"/>
     </row>
     <row r="38" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A38" s="7">
+      <c r="A38" s="6">
         <f t="shared" si="0"/>
         <v>1912</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="7">
         <v>1320</v>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="7">
         <v>1020</v>
       </c>
-      <c r="D38" s="8">
+      <c r="D38" s="7">
         <v>1420</v>
       </c>
-      <c r="E38" s="8">
+      <c r="E38" s="7">
         <v>1120</v>
       </c>
       <c r="F38" s="4"/>
@@ -4178,20 +4178,20 @@
       <c r="AH38" s="3"/>
     </row>
     <row r="39" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A39" s="7">
+      <c r="A39" s="6">
         <f t="shared" si="0"/>
         <v>1913</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="7">
         <v>1330</v>
       </c>
-      <c r="C39" s="8">
+      <c r="C39" s="7">
         <v>1030</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="7">
         <v>1430</v>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="7">
         <v>1130</v>
       </c>
       <c r="F39" s="4"/>
@@ -4205,20 +4205,20 @@
       <c r="AH39" s="3"/>
     </row>
     <row r="40" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A40" s="7">
+      <c r="A40" s="6">
         <f t="shared" si="0"/>
         <v>1914</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="7">
         <v>1340</v>
       </c>
-      <c r="C40" s="8">
+      <c r="C40" s="7">
         <v>1040</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="7">
         <v>1440</v>
       </c>
-      <c r="E40" s="8">
+      <c r="E40" s="7">
         <v>1140</v>
       </c>
       <c r="F40" s="4"/>

--- a/rtss-pre1917/src/main/resources/excel-templates/birth-death-counts-ugvi-csk.xlsx
+++ b/rtss-pre1917/src/main/resources/excel-templates/birth-death-counts-ugvi-csk.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9526782C-27CF-441E-AB4F-CF40893D4DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13217662-7D9F-4E6D-A5CD-8949F44F22A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{552C350D-897F-4D5C-BE01-5853E10F71A5}"/>
+    <workbookView xWindow="13050" yWindow="2160" windowWidth="24945" windowHeight="21255" xr2:uid="{552C350D-897F-4D5C-BE01-5853E10F71A5}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,9 +26,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -90,7 +90,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,7 +203,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$5</c:f>
+              <c:f>data!$B$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -238,7 +238,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$6:$A$40</c:f>
+              <c:f>data!$A$6:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="35"/>
@@ -352,7 +352,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$6:$B$40</c:f>
+              <c:f>data!$B$6:$B$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="35"/>
@@ -476,7 +476,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$5</c:f>
+              <c:f>data!$C$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -517,7 +517,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$6:$A$40</c:f>
+              <c:f>data!$A$6:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="35"/>
@@ -631,7 +631,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$C$6:$C$40</c:f>
+              <c:f>data!$C$6:$C$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="35"/>
@@ -755,7 +755,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$D$5</c:f>
+              <c:f>data!$D$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -790,7 +790,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$6:$A$40</c:f>
+              <c:f>data!$A$6:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="35"/>
@@ -904,7 +904,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$D$6:$D$40</c:f>
+              <c:f>data!$D$6:$D$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="35"/>
@@ -1028,7 +1028,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$E$5</c:f>
+              <c:f>data!$E$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1063,7 +1063,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$6:$A$40</c:f>
+              <c:f>data!$A$6:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="35"/>
@@ -1177,7 +1177,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$6:$E$40</c:f>
+              <c:f>data!$E$6:$E$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="35"/>
@@ -1301,7 +1301,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$G$5</c:f>
+              <c:f>data!$G$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1358,7 +1358,7 @@
           </c:dPt>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$6:$A$40</c:f>
+              <c:f>data!$A$6:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="35"/>
@@ -1472,7 +1472,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$G$6:$G$40</c:f>
+              <c:f>data!$G$6:$G$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="35"/>
@@ -1500,7 +1500,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$H$5</c:f>
+              <c:f>data!$H$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1536,7 +1536,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$6:$A$40</c:f>
+              <c:f>data!$A$6:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="35"/>
@@ -1650,7 +1650,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$H$6:$H$40</c:f>
+              <c:f>data!$H$6:$H$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="35"/>
@@ -1675,7 +1675,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$I$5</c:f>
+              <c:f>data!$I$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1732,7 +1732,7 @@
           </c:dPt>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$6:$A$40</c:f>
+              <c:f>data!$A$6:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="35"/>
@@ -1846,7 +1846,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$I$6:$I$40</c:f>
+              <c:f>data!$I$6:$I$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="35"/>
@@ -1871,7 +1871,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$J$5</c:f>
+              <c:f>data!$J$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1904,7 +1904,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$6:$A$40</c:f>
+              <c:f>data!$A$6:$A$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="35"/>
@@ -2018,7 +2018,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$J$6:$J$40</c:f>
+              <c:f>data!$J$6:$J$40</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="35"/>
@@ -2109,7 +2109,7 @@
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="689771312"/>
@@ -2171,7 +2171,7 @@
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="694533552"/>
@@ -2213,13 +2213,12 @@
               <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2227,6 +2226,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2250,7 +2250,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3176,9 +3176,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ADC5F70-B21E-4A44-9C44-374DD68BE283}">
   <dimension ref="A1:AH41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:34" ht="20.399999999999999" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:34" ht="21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3199,7 +3199,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="3" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:34" ht="15.75">
       <c r="A3" s="4"/>
       <c r="B3" s="8" t="s">
         <v>8</v>
@@ -3215,7 +3215,7 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:34" ht="15.75">
       <c r="A4" s="4"/>
       <c r="B4" s="8" t="s">
         <v>6</v>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="J4" s="8"/>
     </row>
-    <row r="5" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:34" ht="15.75">
       <c r="A5" s="4"/>
       <c r="B5" s="5" t="s">
         <v>2</v>
@@ -3267,7 +3267,7 @@
       <c r="AG5" s="3"/>
       <c r="AH5" s="3"/>
     </row>
-    <row r="6" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:34" ht="15.75">
       <c r="A6" s="6">
         <v>1880</v>
       </c>
@@ -3293,7 +3293,7 @@
       <c r="AG6" s="3"/>
       <c r="AH6" s="3"/>
     </row>
-    <row r="7" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:34" ht="15.75">
       <c r="A7" s="6">
         <f>A6+1</f>
         <v>1881</v>
@@ -3320,7 +3320,7 @@
       <c r="AG7" s="3"/>
       <c r="AH7" s="3"/>
     </row>
-    <row r="8" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:34" ht="15.75">
       <c r="A8" s="6">
         <f t="shared" ref="A8:A40" si="0">A7+1</f>
         <v>1882</v>
@@ -3347,7 +3347,7 @@
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
     </row>
-    <row r="9" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:34" ht="15.75">
       <c r="A9" s="6">
         <f t="shared" si="0"/>
         <v>1883</v>
@@ -3374,7 +3374,7 @@
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
     </row>
-    <row r="10" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:34" ht="15.75">
       <c r="A10" s="6">
         <f t="shared" si="0"/>
         <v>1884</v>
@@ -3401,7 +3401,7 @@
       <c r="AG10" s="3"/>
       <c r="AH10" s="3"/>
     </row>
-    <row r="11" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:34" ht="15.75">
       <c r="A11" s="6">
         <f t="shared" si="0"/>
         <v>1885</v>
@@ -3436,7 +3436,7 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
     </row>
-    <row r="12" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:34" ht="15.75">
       <c r="A12" s="6">
         <f t="shared" si="0"/>
         <v>1886</v>
@@ -3471,7 +3471,7 @@
       <c r="AG12" s="3"/>
       <c r="AH12" s="3"/>
     </row>
-    <row r="13" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:34" ht="15.75">
       <c r="A13" s="6">
         <f t="shared" si="0"/>
         <v>1887</v>
@@ -3502,7 +3502,7 @@
       <c r="AG13" s="3"/>
       <c r="AH13" s="3"/>
     </row>
-    <row r="14" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:34" ht="15.75">
       <c r="A14" s="6">
         <f t="shared" si="0"/>
         <v>1888</v>
@@ -3529,7 +3529,7 @@
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
     </row>
-    <row r="15" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:34" ht="15.75">
       <c r="A15" s="6">
         <f t="shared" si="0"/>
         <v>1889</v>
@@ -3556,7 +3556,7 @@
       <c r="AG15" s="3"/>
       <c r="AH15" s="3"/>
     </row>
-    <row r="16" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:34" ht="15.75">
       <c r="A16" s="6">
         <f t="shared" si="0"/>
         <v>1890</v>
@@ -3583,7 +3583,7 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
     </row>
-    <row r="17" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:34" ht="15.75">
       <c r="A17" s="6">
         <f t="shared" si="0"/>
         <v>1891</v>
@@ -3610,7 +3610,7 @@
       <c r="AG17" s="3"/>
       <c r="AH17" s="3"/>
     </row>
-    <row r="18" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:34" ht="15.75">
       <c r="A18" s="6">
         <f t="shared" si="0"/>
         <v>1892</v>
@@ -3637,7 +3637,7 @@
       <c r="AG18" s="3"/>
       <c r="AH18" s="3"/>
     </row>
-    <row r="19" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:34" ht="15.75">
       <c r="A19" s="6">
         <f t="shared" si="0"/>
         <v>1893</v>
@@ -3664,7 +3664,7 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
     </row>
-    <row r="20" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:34" ht="15.75">
       <c r="A20" s="6">
         <f t="shared" si="0"/>
         <v>1894</v>
@@ -3691,7 +3691,7 @@
       <c r="AG20" s="3"/>
       <c r="AH20" s="3"/>
     </row>
-    <row r="21" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:34" ht="15.75">
       <c r="A21" s="6">
         <f t="shared" si="0"/>
         <v>1895</v>
@@ -3718,7 +3718,7 @@
       <c r="AG21" s="3"/>
       <c r="AH21" s="3"/>
     </row>
-    <row r="22" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:34" ht="15.75">
       <c r="A22" s="6">
         <f t="shared" si="0"/>
         <v>1896</v>
@@ -3745,7 +3745,7 @@
       <c r="AG22" s="3"/>
       <c r="AH22" s="3"/>
     </row>
-    <row r="23" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:34" ht="15.75">
       <c r="A23" s="6">
         <f t="shared" si="0"/>
         <v>1897</v>
@@ -3772,7 +3772,7 @@
       <c r="AG23" s="3"/>
       <c r="AH23" s="3"/>
     </row>
-    <row r="24" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:34" ht="15.75">
       <c r="A24" s="6">
         <f t="shared" si="0"/>
         <v>1898</v>
@@ -3799,7 +3799,7 @@
       <c r="AG24" s="3"/>
       <c r="AH24" s="3"/>
     </row>
-    <row r="25" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:34" ht="15.75">
       <c r="A25" s="6">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -3826,7 +3826,7 @@
       <c r="AG25" s="3"/>
       <c r="AH25" s="3"/>
     </row>
-    <row r="26" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:34" ht="15.75">
       <c r="A26" s="6">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -3853,7 +3853,7 @@
       <c r="AG26" s="3"/>
       <c r="AH26" s="3"/>
     </row>
-    <row r="27" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:34" ht="15.75">
       <c r="A27" s="6">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -3880,7 +3880,7 @@
       <c r="AG27" s="3"/>
       <c r="AH27" s="3"/>
     </row>
-    <row r="28" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:34" ht="15.75">
       <c r="A28" s="6">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -3907,7 +3907,7 @@
       <c r="AG28" s="3"/>
       <c r="AH28" s="3"/>
     </row>
-    <row r="29" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:34" ht="15.75">
       <c r="A29" s="6">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -3934,7 +3934,7 @@
       <c r="AG29" s="3"/>
       <c r="AH29" s="3"/>
     </row>
-    <row r="30" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:34" ht="15.75">
       <c r="A30" s="6">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -3961,7 +3961,7 @@
       <c r="AG30" s="3"/>
       <c r="AH30" s="3"/>
     </row>
-    <row r="31" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:34" ht="15.75">
       <c r="A31" s="6">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -3988,7 +3988,7 @@
       <c r="AG31" s="3"/>
       <c r="AH31" s="3"/>
     </row>
-    <row r="32" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:34" ht="15.75">
       <c r="A32" s="6">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -4015,7 +4015,7 @@
       <c r="AG32" s="3"/>
       <c r="AH32" s="3"/>
     </row>
-    <row r="33" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:34" ht="15.75">
       <c r="A33" s="6">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -4042,7 +4042,7 @@
       <c r="AG33" s="3"/>
       <c r="AH33" s="3"/>
     </row>
-    <row r="34" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:34" ht="15.75">
       <c r="A34" s="6">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -4069,7 +4069,7 @@
       <c r="AG34" s="3"/>
       <c r="AH34" s="3"/>
     </row>
-    <row r="35" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:34" ht="15.75">
       <c r="A35" s="6">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -4096,7 +4096,7 @@
       <c r="AG35" s="3"/>
       <c r="AH35" s="3"/>
     </row>
-    <row r="36" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:34" ht="15.75">
       <c r="A36" s="6">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -4123,7 +4123,7 @@
       <c r="AG36" s="3"/>
       <c r="AH36" s="3"/>
     </row>
-    <row r="37" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:34" ht="15.75">
       <c r="A37" s="6">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -4150,7 +4150,7 @@
       <c r="AG37" s="3"/>
       <c r="AH37" s="3"/>
     </row>
-    <row r="38" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:34" ht="15.75">
       <c r="A38" s="6">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -4177,7 +4177,7 @@
       <c r="AG38" s="3"/>
       <c r="AH38" s="3"/>
     </row>
-    <row r="39" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:34" ht="15.75">
       <c r="A39" s="6">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -4204,7 +4204,7 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
     </row>
-    <row r="40" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:34" ht="15.75">
       <c r="A40" s="6">
         <f t="shared" si="0"/>
         <v>1914</v>
@@ -4227,7 +4227,7 @@
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" spans="1:34" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:34" ht="15.75">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>

--- a/rtss-pre1917/src/main/resources/excel-templates/birth-death-counts-ugvi-csk.xlsx
+++ b/rtss-pre1917/src/main/resources/excel-templates/birth-death-counts-ugvi-csk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13217662-7D9F-4E6D-A5CD-8949F44F22A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1A47A2-FF2B-43C1-8331-E28057919178}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13050" yWindow="2160" windowWidth="24945" windowHeight="21255" xr2:uid="{552C350D-897F-4D5C-BE01-5853E10F71A5}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{552C350D-897F-4D5C-BE01-5853E10F71A5}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -145,21 +145,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1474,12 +1482,12 @@
             <c:numRef>
               <c:f>data!$G$6:$G$40</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="35"/>
-                <c:pt idx="5" formatCode="#,##0">
+                <c:pt idx="5">
                   <c:v>1200</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="#,##0">
+                <c:pt idx="6">
                   <c:v>1500</c:v>
                 </c:pt>
                 <c:pt idx="7">
@@ -1652,12 +1660,12 @@
             <c:numRef>
               <c:f>data!$H$6:$H$40</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="35"/>
-                <c:pt idx="5" formatCode="#,##0">
+                <c:pt idx="5">
                   <c:v>1350</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="#,##0">
+                <c:pt idx="6">
                   <c:v>1200</c:v>
                 </c:pt>
               </c:numCache>
@@ -1848,12 +1856,12 @@
             <c:numRef>
               <c:f>data!$I$6:$I$40</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="35"/>
-                <c:pt idx="5" formatCode="#,##0">
+                <c:pt idx="5">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="6" formatCode="#,##0">
+                <c:pt idx="6">
                   <c:v>1200</c:v>
                 </c:pt>
               </c:numCache>
@@ -2020,9 +2028,9 @@
             <c:numRef>
               <c:f>data!$J$6:$J$40</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="35"/>
-                <c:pt idx="5" formatCode="#,##0">
+                <c:pt idx="5">
                   <c:v>1250</c:v>
                 </c:pt>
                 <c:pt idx="6">
@@ -3199,15 +3207,27 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
+    <row r="2" spans="1:34">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+    </row>
     <row r="3" spans="1:34" ht="15.75">
-      <c r="A3" s="4"/>
+      <c r="A3" s="7"/>
       <c r="B3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
-      <c r="F3" s="4"/>
+      <c r="F3" s="7"/>
       <c r="G3" s="8" t="s">
         <v>14</v>
       </c>
@@ -3216,7 +3236,7 @@
       <c r="J3" s="8"/>
     </row>
     <row r="4" spans="1:34" ht="15.75">
-      <c r="A4" s="4"/>
+      <c r="A4" s="7"/>
       <c r="B4" s="8" t="s">
         <v>6</v>
       </c>
@@ -3225,7 +3245,7 @@
         <v>7</v>
       </c>
       <c r="E4" s="8"/>
-      <c r="F4" s="4"/>
+      <c r="F4" s="7"/>
       <c r="G4" s="8" t="s">
         <v>6</v>
       </c>
@@ -3236,30 +3256,30 @@
       <c r="J4" s="8"/>
     </row>
     <row r="5" spans="1:34" ht="15.75">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="7"/>
+      <c r="B5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="7"/>
+      <c r="G5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="9" t="s">
         <v>12</v>
       </c>
       <c r="AE5" s="3"/>
@@ -3268,167 +3288,167 @@
       <c r="AH5" s="3"/>
     </row>
     <row r="6" spans="1:34" ht="15.75">
-      <c r="A6" s="6">
+      <c r="A6" s="10">
         <v>1880</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>1000</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>700</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>1100</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>800</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="3"/>
       <c r="AH6" s="3"/>
     </row>
     <row r="7" spans="1:34" ht="15.75">
-      <c r="A7" s="6">
+      <c r="A7" s="10">
         <f>A6+1</f>
         <v>1881</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>1010</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>710</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>1110</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <v>810</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
       <c r="AG7" s="3"/>
       <c r="AH7" s="3"/>
     </row>
     <row r="8" spans="1:34" ht="15.75">
-      <c r="A8" s="6">
+      <c r="A8" s="10">
         <f t="shared" ref="A8:A40" si="0">A7+1</f>
         <v>1882</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>1020</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>720</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <v>1120</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <v>820</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
       <c r="AE8" s="3"/>
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
     </row>
     <row r="9" spans="1:34" ht="15.75">
-      <c r="A9" s="6">
+      <c r="A9" s="10">
         <f t="shared" si="0"/>
         <v>1883</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <v>1030</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="5">
         <v>730</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="5">
         <v>1130</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="5">
         <v>830</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
     </row>
     <row r="10" spans="1:34" ht="15.75">
-      <c r="A10" s="6">
+      <c r="A10" s="10">
         <f t="shared" si="0"/>
         <v>1884</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>1040</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>740</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <v>1140</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <v>840</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
       <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
       <c r="AG10" s="3"/>
       <c r="AH10" s="3"/>
     </row>
     <row r="11" spans="1:34" ht="15.75">
-      <c r="A11" s="6">
+      <c r="A11" s="10">
         <f t="shared" si="0"/>
         <v>1885</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="5">
         <v>1050</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="5">
         <v>750</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="5">
         <v>1150</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
         <v>850</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="7">
+      <c r="F11" s="7"/>
+      <c r="G11" s="5">
         <v>1200</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="5">
         <v>1350</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="5">
         <v>900</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="5">
         <v>1250</v>
       </c>
       <c r="AE11" s="3"/>
@@ -3437,33 +3457,33 @@
       <c r="AH11" s="3"/>
     </row>
     <row r="12" spans="1:34" ht="15.75">
-      <c r="A12" s="6">
+      <c r="A12" s="10">
         <f t="shared" si="0"/>
         <v>1886</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="5">
         <v>1060</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <v>760</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <v>1160</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <v>860</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="7">
+      <c r="F12" s="7"/>
+      <c r="G12" s="5">
         <v>1500</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="5">
         <v>1200</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="5">
         <v>1200</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="5">
         <v>1500</v>
       </c>
       <c r="AE12" s="3"/>
@@ -3472,29 +3492,29 @@
       <c r="AH12" s="3"/>
     </row>
     <row r="13" spans="1:34" ht="15.75">
-      <c r="A13" s="6">
+      <c r="A13" s="10">
         <f t="shared" si="0"/>
         <v>1887</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="5">
         <v>1070</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="5">
         <v>770</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <v>1170</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="5">
         <v>870</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="7"/>
+      <c r="G13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4">
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5">
         <v>1550</v>
       </c>
       <c r="AE13" s="3"/>
@@ -3503,729 +3523,729 @@
       <c r="AH13" s="3"/>
     </row>
     <row r="14" spans="1:34" ht="15.75">
-      <c r="A14" s="6">
+      <c r="A14" s="10">
         <f t="shared" si="0"/>
         <v>1888</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="5">
         <v>1080</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <v>780</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <v>1180</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="5">
         <v>880</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
     </row>
     <row r="15" spans="1:34" ht="15.75">
-      <c r="A15" s="6">
+      <c r="A15" s="10">
         <f t="shared" si="0"/>
         <v>1889</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="5">
         <v>1090</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="5">
         <v>790</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="5">
         <v>1190</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="5">
         <v>890</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
       <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
       <c r="AG15" s="3"/>
       <c r="AH15" s="3"/>
     </row>
     <row r="16" spans="1:34" ht="15.75">
-      <c r="A16" s="6">
+      <c r="A16" s="10">
         <f t="shared" si="0"/>
         <v>1890</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="5">
         <v>1100</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>800</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="5">
         <v>1200</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="5">
         <v>900</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
     </row>
     <row r="17" spans="1:34" ht="15.75">
-      <c r="A17" s="6">
+      <c r="A17" s="10">
         <f t="shared" si="0"/>
         <v>1891</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="5">
         <v>1110</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <v>810</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <v>1210</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="5">
         <v>910</v>
       </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
       <c r="AE17" s="3"/>
       <c r="AF17" s="3"/>
       <c r="AG17" s="3"/>
       <c r="AH17" s="3"/>
     </row>
     <row r="18" spans="1:34" ht="15.75">
-      <c r="A18" s="6">
+      <c r="A18" s="10">
         <f t="shared" si="0"/>
         <v>1892</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="5">
         <v>1120</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="5">
         <v>820</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="5">
         <v>1220</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="5">
         <v>920</v>
       </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
       <c r="AE18" s="3"/>
       <c r="AF18" s="3"/>
       <c r="AG18" s="3"/>
       <c r="AH18" s="3"/>
     </row>
     <row r="19" spans="1:34" ht="15.75">
-      <c r="A19" s="6">
+      <c r="A19" s="10">
         <f t="shared" si="0"/>
         <v>1893</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="5">
         <v>1130</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="5">
         <v>830</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="5">
         <v>1230</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="5">
         <v>930</v>
       </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
     </row>
     <row r="20" spans="1:34" ht="15.75">
-      <c r="A20" s="6">
+      <c r="A20" s="10">
         <f t="shared" si="0"/>
         <v>1894</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="5">
         <v>1140</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="5">
         <v>840</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="5">
         <v>1240</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="5">
         <v>940</v>
       </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
       <c r="AE20" s="3"/>
       <c r="AF20" s="3"/>
       <c r="AG20" s="3"/>
       <c r="AH20" s="3"/>
     </row>
     <row r="21" spans="1:34" ht="15.75">
-      <c r="A21" s="6">
+      <c r="A21" s="10">
         <f t="shared" si="0"/>
         <v>1895</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="5">
         <v>1150</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="5">
         <v>850</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="5">
         <v>1250</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="5">
         <v>950</v>
       </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
       <c r="AE21" s="3"/>
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
       <c r="AH21" s="3"/>
     </row>
     <row r="22" spans="1:34" ht="15.75">
-      <c r="A22" s="6">
+      <c r="A22" s="10">
         <f t="shared" si="0"/>
         <v>1896</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="5">
         <v>1160</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="5">
         <v>860</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="5">
         <v>1260</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="5">
         <v>960</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
       <c r="AE22" s="3"/>
       <c r="AF22" s="3"/>
       <c r="AG22" s="3"/>
       <c r="AH22" s="3"/>
     </row>
     <row r="23" spans="1:34" ht="15.75">
-      <c r="A23" s="6">
+      <c r="A23" s="10">
         <f t="shared" si="0"/>
         <v>1897</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="5">
         <v>1170</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="5">
         <v>870</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="5">
         <v>1270</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="5">
         <v>970</v>
       </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
       <c r="AE23" s="3"/>
       <c r="AF23" s="3"/>
       <c r="AG23" s="3"/>
       <c r="AH23" s="3"/>
     </row>
     <row r="24" spans="1:34" ht="15.75">
-      <c r="A24" s="6">
+      <c r="A24" s="10">
         <f t="shared" si="0"/>
         <v>1898</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="5">
         <v>1180</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="5">
         <v>880</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="5">
         <v>1280</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="5">
         <v>980</v>
       </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
       <c r="AE24" s="3"/>
       <c r="AF24" s="3"/>
       <c r="AG24" s="3"/>
       <c r="AH24" s="3"/>
     </row>
     <row r="25" spans="1:34" ht="15.75">
-      <c r="A25" s="6">
+      <c r="A25" s="10">
         <f t="shared" si="0"/>
         <v>1899</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="5">
         <v>1190</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="5">
         <v>890</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="5">
         <v>1290</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="5">
         <v>990</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
       <c r="AG25" s="3"/>
       <c r="AH25" s="3"/>
     </row>
     <row r="26" spans="1:34" ht="15.75">
-      <c r="A26" s="6">
+      <c r="A26" s="10">
         <f t="shared" si="0"/>
         <v>1900</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="5">
         <v>1200</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="5">
         <v>900</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="5">
         <v>1300</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="5">
         <v>1000</v>
       </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
       <c r="AE26" s="3"/>
       <c r="AF26" s="3"/>
       <c r="AG26" s="3"/>
       <c r="AH26" s="3"/>
     </row>
     <row r="27" spans="1:34" ht="15.75">
-      <c r="A27" s="6">
+      <c r="A27" s="10">
         <f t="shared" si="0"/>
         <v>1901</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="5">
         <v>1210</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="5">
         <v>910</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="5">
         <v>1310</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="5">
         <v>1010</v>
       </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
       <c r="AE27" s="3"/>
       <c r="AF27" s="3"/>
       <c r="AG27" s="3"/>
       <c r="AH27" s="3"/>
     </row>
     <row r="28" spans="1:34" ht="15.75">
-      <c r="A28" s="6">
+      <c r="A28" s="10">
         <f t="shared" si="0"/>
         <v>1902</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="5">
         <v>1220</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="5">
         <v>920</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="5">
         <v>1320</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="5">
         <v>1020</v>
       </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
       <c r="AE28" s="3"/>
       <c r="AF28" s="3"/>
       <c r="AG28" s="3"/>
       <c r="AH28" s="3"/>
     </row>
     <row r="29" spans="1:34" ht="15.75">
-      <c r="A29" s="6">
+      <c r="A29" s="10">
         <f t="shared" si="0"/>
         <v>1903</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="5">
         <v>1230</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="5">
         <v>930</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="5">
         <v>1330</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="5">
         <v>1030</v>
       </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
       <c r="AG29" s="3"/>
       <c r="AH29" s="3"/>
     </row>
     <row r="30" spans="1:34" ht="15.75">
-      <c r="A30" s="6">
+      <c r="A30" s="10">
         <f t="shared" si="0"/>
         <v>1904</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="5">
         <v>1240</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="5">
         <v>940</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="5">
         <v>1340</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="5">
         <v>1040</v>
       </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
       <c r="AG30" s="3"/>
       <c r="AH30" s="3"/>
     </row>
     <row r="31" spans="1:34" ht="15.75">
-      <c r="A31" s="6">
+      <c r="A31" s="10">
         <f t="shared" si="0"/>
         <v>1905</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="5">
         <v>1250</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="5">
         <v>950</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="5">
         <v>1350</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="5">
         <v>1050</v>
       </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
       <c r="AE31" s="3"/>
       <c r="AF31" s="3"/>
       <c r="AG31" s="3"/>
       <c r="AH31" s="3"/>
     </row>
     <row r="32" spans="1:34" ht="15.75">
-      <c r="A32" s="6">
+      <c r="A32" s="10">
         <f t="shared" si="0"/>
         <v>1906</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="5">
         <v>1260</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="5">
         <v>960</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="5">
         <v>1360</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="5">
         <v>1060</v>
       </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
       <c r="AE32" s="3"/>
       <c r="AF32" s="3"/>
       <c r="AG32" s="3"/>
       <c r="AH32" s="3"/>
     </row>
     <row r="33" spans="1:34" ht="15.75">
-      <c r="A33" s="6">
+      <c r="A33" s="10">
         <f t="shared" si="0"/>
         <v>1907</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="5">
         <v>1270</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="5">
         <v>970</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="5">
         <v>1370</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="5">
         <v>1070</v>
       </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
       <c r="AE33" s="3"/>
       <c r="AF33" s="3"/>
       <c r="AG33" s="3"/>
       <c r="AH33" s="3"/>
     </row>
     <row r="34" spans="1:34" ht="15.75">
-      <c r="A34" s="6">
+      <c r="A34" s="10">
         <f t="shared" si="0"/>
         <v>1908</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="5">
         <v>1280</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="5">
         <v>980</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="5">
         <v>1380</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="5">
         <v>1080</v>
       </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
       <c r="AE34" s="3"/>
       <c r="AF34" s="3"/>
       <c r="AG34" s="3"/>
       <c r="AH34" s="3"/>
     </row>
     <row r="35" spans="1:34" ht="15.75">
-      <c r="A35" s="6">
+      <c r="A35" s="10">
         <f t="shared" si="0"/>
         <v>1909</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="5">
         <v>1290</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="5">
         <v>990</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="5">
         <v>1390</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="5">
         <v>1090</v>
       </c>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
       <c r="AE35" s="3"/>
       <c r="AF35" s="3"/>
       <c r="AG35" s="3"/>
       <c r="AH35" s="3"/>
     </row>
     <row r="36" spans="1:34" ht="15.75">
-      <c r="A36" s="6">
+      <c r="A36" s="10">
         <f t="shared" si="0"/>
         <v>1910</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="5">
         <v>1300</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="5">
         <v>1000</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="5">
         <v>1400</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="5">
         <v>1100</v>
       </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
       <c r="AE36" s="3"/>
       <c r="AF36" s="3"/>
       <c r="AG36" s="3"/>
       <c r="AH36" s="3"/>
     </row>
     <row r="37" spans="1:34" ht="15.75">
-      <c r="A37" s="6">
+      <c r="A37" s="10">
         <f t="shared" si="0"/>
         <v>1911</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="5">
         <v>1310</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="5">
         <v>1010</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="5">
         <v>1410</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="5">
         <v>1110</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
       <c r="AE37" s="3"/>
       <c r="AF37" s="3"/>
       <c r="AG37" s="3"/>
       <c r="AH37" s="3"/>
     </row>
     <row r="38" spans="1:34" ht="15.75">
-      <c r="A38" s="6">
+      <c r="A38" s="10">
         <f t="shared" si="0"/>
         <v>1912</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="5">
         <v>1320</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="5">
         <v>1020</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="5">
         <v>1420</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="5">
         <v>1120</v>
       </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
       <c r="AE38" s="3"/>
       <c r="AF38" s="3"/>
       <c r="AG38" s="3"/>
       <c r="AH38" s="3"/>
     </row>
     <row r="39" spans="1:34" ht="15.75">
-      <c r="A39" s="6">
+      <c r="A39" s="10">
         <f t="shared" si="0"/>
         <v>1913</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="5">
         <v>1330</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="5">
         <v>1030</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="5">
         <v>1430</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="5">
         <v>1130</v>
       </c>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
     </row>
     <row r="40" spans="1:34" ht="15.75">
-      <c r="A40" s="6">
+      <c r="A40" s="10">
         <f t="shared" si="0"/>
         <v>1914</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="5">
         <v>1340</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="5">
         <v>1040</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="5">
         <v>1440</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E40" s="5">
         <v>1140</v>
       </c>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
     </row>
     <row r="41" spans="1:34" ht="15.75">
       <c r="A41" s="4"/>
@@ -4249,7 +4269,8 @@
     <mergeCell ref="G3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
